--- a/venture/07-automation/tracker/publish-queue/simple-budget-starter-v1/10-Minute-Simple-Budget.xlsx
+++ b/venture/07-automation/tracker/publish-queue/simple-budget-starter-v1/10-Minute-Simple-Budget.xlsx
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00;($#,##0.00)"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -140,8 +141,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -262,6 +263,147 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Planned vs Spent — your 10 lines</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Monthly Budget'!C12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F3A5F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Monthly Budget'!$B$13:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Monthly Budget'!$C$13:$C$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Monthly Budget'!D12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="F2C14E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Monthly Budget'!$B$13:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Monthly Budget'!$D$13:$D$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -551,9 +693,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E21"/>
+  <dimension ref="B2:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -621,7 +763,7 @@
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3. 'Bill Calendar' tab: type an x when you pay a bill — the box turns green. That's it.</t>
+          <t>3. 'Bill Calendar' tab: pick the x from the dropdown when you pay a bill — the box turns green. That's it.</t>
         </is>
       </c>
     </row>
@@ -667,10 +809,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>The dropdowns and the little Planned-vs-Spent chart convert too; chart colors may shift slightly. Numbers are identical.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Questions or a formula acting up? Message us on Etsy any time — we answer fast and we'll fix it.</t>
         </is>
@@ -684,6 +833,7 @@
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -691,7 +841,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1039,6 +1189,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1046,7 +1198,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1079,7 +1231,7 @@
     <row r="4">
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Type an x when a bill is paid — the box turns green. January is a worked example; clear it and start with your month.</t>
+          <t>Pick the x from the dropdown when a bill is paid — the box turns green. January is a worked example; clear it and start with your month.</t>
         </is>
       </c>
     </row>
@@ -1725,6 +1877,12 @@
       <formula>"x"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E7:P26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Paid marker" error="Pick x from the dropdown (or leave the box blank)." promptTitle="Paid?" prompt="Pick x when this bill is paid." type="list">
+      <formula1>"x"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>